--- a/applications_tracker.xlsx
+++ b/applications_tracker.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$R$55</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +27,35 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +70,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,439 +440,2583 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="81" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="110" customWidth="1" min="13" max="13"/>
+    <col width="51" customWidth="1" min="14" max="14"/>
+    <col width="66" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="44" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Date Applied</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Follow-up Date</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Work Mode</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Technologies</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Focus Area</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Focus</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Paid</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>NTT Data</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Spain - A Coruña</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Applied</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>IT internship</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Spain - Getafe</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Applied</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Engineering / Stress team</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Portugal - Porto</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Azure DevOps Trainee (m/f/d)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Applied</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Cloud / DevOps / Azure</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Portugal - Lisbon</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>IT Trainee</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Applied</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>IT Systems</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Spain - Valencia</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Prácticas en Ciberseguridad</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Applied</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Cybersecurity internship</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>NTT Data</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Spain - A Coruña</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>iAgora</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Applied</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>IT internship</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Spain - Getafe</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>iAgora</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Applied</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Engineering / Stress team</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Portugal - Porto</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Azure DevOps Trainee (m/f/d)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>iAgora</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Applied</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>Cloud / DevOps / Azure</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Airbus</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Portugal - Lisbon</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>IT Trainee</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>iAgora</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Applied</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>IT Systems</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Capgemini</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Spain - Valencia</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Prácticas en Ciberseguridad</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>iAgora</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Applied</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Cybersecurity internship</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Internship (Insurance / Business / IT - unspecified)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Applied via iAgora - Zurich Spain internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Internship (Insurance / Business / IT - unspecified)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Applied via iAgora - Zurich Spain internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/applications_tracker.xlsx
+++ b/applications_tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$R$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$R$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,10 +440,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:R184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="81" customWidth="1" min="4" max="4"/>
@@ -451,7 +451,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="80" customWidth="1" min="9" max="9"/>
+    <col width="103" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
@@ -3015,8 +3015,6298 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G168" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G178" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G181" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R55"/>
+  <autoFilter ref="A1:R184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/applications_tracker.xlsx
+++ b/applications_tracker.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$R$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$R$259</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -70,11 +73,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R184"/>
+  <dimension ref="A1:R263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9305,8 +9309,3269 @@
         </is>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G187" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G188" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G191" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="G212" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="G227" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="G229" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="G244" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="G246" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>NTT Data</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Spain - A Coruña</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>IT internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Spain - Getafe</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>#Discover II 2026-2027 Internship FDT Stress Team</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Engineering / Stress team</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Portugal - Porto</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Azure DevOps Trainee (m/f/d)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Cloud / DevOps / Azure</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Portugal - Lisbon</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>IT Trainee</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>IT Systems</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Spain - Valencia</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Prácticas en Ciberseguridad</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Cybersecurity internship</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Bosch</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Data Engineering Internship (Lakehouse / Databricks)</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>iAgora</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Data engineering, cloud, Hadoop to Databricks migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Zurich Insurance</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Trainee Cloud Application Developer - 133025</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Zurich Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Application rejected after recruitment process review</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Cloud Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Telecommunication Support Trainee - Global Core Network Team</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>iAgora / Job Portal</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Strong technical telecom role with exposure to cloud and network core systems</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>International / Hybrid</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Telecommunications / Cloud / Network Engineering</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Siemens</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Siemens Talents Hub Internship 2026 - Data Analytics &amp; Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>iAgora / Siemens Careers</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>R&amp;D internship in AI and Data Analytics</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Brasov / Cluj-Napoca / Bucharest</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Novo Nordisk</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>BI, Data &amp; AI Intern - Complaint Insights Team</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Career Portal / Application Form</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>BI + AI internship focused on healthcare data analytics</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Bagsværd</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Prácticas Ingeniería Informática - Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>NTT DATA Careers / iAgora</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Application confirmed by NTT DATA recruitment team via email</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>A Coruña</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>BECAS BBVA ÁREAS DE TECNOLOGÍA E INNOVACIÓN 2026</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>BBVA Careers</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Natixis</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>IT Trainee | WE WANT YOU 2026 S2</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Natixis Careers</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Porto / Lisbon</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="260"/>
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>Total Rechazadas:</t>
+        </is>
+      </c>
+      <c r="G261" s="4" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>Total Aplicadas:</t>
+        </is>
+      </c>
+      <c r="G263" s="4" t="n">
+        <v>180</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R184"/>
+  <autoFilter ref="A1:R259"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/applications_tracker.xlsx
+++ b/applications_tracker.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,50 +1177,52 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="16"/>
+    <row r="17"/>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>JOB TRACKER DASHBOARD</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Total Applications</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Applied</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rejected</t>
+          <t>Total Applications</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B24" t="n">
         <v>0</v>
       </c>
     </row>

--- a/applications_tracker.xlsx
+++ b/applications_tracker.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,10 +27,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
     </font>
   </fonts>
   <fills count="4">
@@ -43,11 +39,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,12 +61,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,45 +477,40 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Follow-up Date</t>
+          <t>Focus</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Focus</t>
+          <t>City</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Work Mode</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Work Mode</t>
+          <t>Technologies</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Technologies</t>
+          <t>Focus Area</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Focus Area</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Paid</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Tools</t>
         </is>
@@ -777,7 +769,7 @@
           <t>Application rejected after recruitment process review</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Cloud Development</t>
         </is>
@@ -819,22 +811,22 @@
           <t>Strong technical telecom role with exposure to cloud and network core systems</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Portugal (location not specified)</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Portugal (location not specified)</t>
+          <t>International / Hybrid</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>International / Hybrid</t>
+          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
-        <is>
-          <t>['IMS Voice', 'Packet Core', 'Cloud Infrastructure', 'Linux', 'OpenStack', '3GPP', 'VoLTE / VoWiFi / Vo5G']</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
         <is>
           <t>Telecommunications / Cloud / Network Engineering</t>
         </is>
@@ -876,22 +868,22 @@
           <t>R&amp;D internship in AI and Data Analytics</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AI, Data Analytics, R&amp;D, Machine Learning, Software Prototyping</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
           <t>Brasov / Cluj-Napoca / Bucharest</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3 months</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
-        <is>
-          <t>3 months</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -933,27 +925,27 @@
           <t>BI + AI internship focused on healthcare data analytics</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Business Intelligence, Data Analytics, AI, Power BI</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
           <t>Bagsværd</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
         <is>
           <t>['Power BI', 'Python', 'SQL', 'AI tools']</t>
         </is>
@@ -995,17 +987,17 @@
           <t>Application confirmed by NTT DATA recruitment team via email</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Software Development, Telecommunications, IT</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Software Development, Telecommunications, IT</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
           <t>A Coruña</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -1047,17 +1039,17 @@
           <t>Scholarship/internship application confirmed by BBVA recruitment team</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Technology, Innovation, IT</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Technology, Innovation, IT</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
           <t>Madrid</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -1099,22 +1091,22 @@
           <t>International trainee program focused on IT, software development, data, cybersecurity and analytics</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>IT Trainee Program, Development, Data, Cybersecurity, DevOps</t>
+          <t>Porto / Lisbon</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Porto / Lisbon</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
           <t>Hybrid</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
@@ -1156,74 +1148,109 @@
           <t>Student role focused on Product Security, vulnerability management and secure development practices in a global tech environment. Strong interest in cybersecurity and hands-on learning.</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Remote / Hybrid (Portugal / Europe)</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Remote / Hybrid (Portugal / Europe)</t>
+          <t>Hybrid / Remote</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Hybrid / Remote</t>
+          <t>['Secure Software Development Lifecycle (S-SDLC)', 'Vulnerability Management', 'Software Architecture', 'Programming', 'Databases', 'Application Security']</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>['Secure Software Development Lifecycle (S-SDLC)', 'Vulnerability Management', 'Software Architecture', 'Programming', 'Databases', 'Application Security']</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
           <t>Product Security / Cybersecurity / Secure Software Development</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Technology Summer Internship</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Accenture Careers</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Req ID: R00321525 | Application received</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>JOB TRACKER DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Total:</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>15</v>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>JOB TRACKER DASHBOARD</t>
-        </is>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Applied:</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Total Applications</t>
+          <t>Rejected:</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Applied</t>
+          <t>Pending:</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
